--- a/tests/data/module_test.xlsx
+++ b/tests/data/module_test.xlsx
@@ -57,7 +57,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Total area of the substrate</t>
+          <t xml:space="preserve">Active area of each individual pixel/cell</t>
         </r>
       </text>
     </comment>
@@ -69,7 +69,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Number of individual solar cell pixels on the substrate</t>
+          <t xml:space="preserve">Active area of each pixel/cell. Equal to pixel area if no mask</t>
         </r>
       </text>
     </comment>
@@ -81,11 +81,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Active area of each individual pixel</t>
+          <t xml:space="preserve">Interconnects etc dead area of each pixel/cell</t>
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Number of individual solar cell pixels on the substrate</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t xml:space="preserve">Experiment Info</t>
   </si>
@@ -133,13 +145,28 @@
     <t xml:space="preserve">Sample dimension</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample area [cm^2]</t>
+    <t xml:space="preserve">Pixel area [cm^2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active area [cm^2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead area [cm^2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geometrical fill factor</t>
   </si>
   <si>
     <t xml:space="preserve">Number of pixels</t>
   </si>
   <si>
-    <t xml:space="preserve">Pixel area [cm^2]</t>
+    <t xml:space="preserve">Is module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel/cell connection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module dimension after encapsulation</t>
   </si>
   <si>
     <t xml:space="preserve">Substrate material</t>
@@ -163,21 +190,6 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Is module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel connection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active area [cm^2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dead area [cm^2]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geometrical fill factor</t>
-  </si>
-  <si>
     <t xml:space="preserve">21-05-2025</t>
   </si>
   <si>
@@ -193,6 +205,12 @@
     <t xml:space="preserve">1 cm x 1 cm</t>
   </si>
   <si>
+    <t xml:space="preserve">parallel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 x 16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Soda Lime Glass</t>
   </si>
   <si>
@@ -200,9 +218,6 @@
   </si>
   <si>
     <t xml:space="preserve">Experiment Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parallel</t>
   </si>
 </sst>
 </file>
@@ -584,20 +599,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="17.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16372" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -621,6 +637,11 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
@@ -723,52 +744,52 @@
         <v>0.16</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="O3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="S3" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="U3" s="1" t="n">
-        <v>0.9</v>
+        <v>150</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W3" s="1" t="n">
-        <v>0.9</v>
+        <v>1</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
